--- a/games/life/data/specialthanks-afd.xlsx
+++ b/games/life/data/specialthanks-afd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\84694\Desktop\人生重来\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA67E60-5BED-41CA-8135-C70A8703B3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269F04D8-F596-496A-BF00-B8BE09FA7437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="590">
   <si>
     <t>group</t>
   </si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>shiki</t>
-  </si>
-  <si>
-    <t>小羊</t>
   </si>
   <si>
     <t>狂啸</t>
@@ -1204,6 +1201,964 @@
   </si>
   <si>
     <t>我是原P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>煮饭233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千里未来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>haooo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闵佳瑶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿婆朱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>油腻的Wink😉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带你嫖娼的馆长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obento</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银子舟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大户爱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冥渊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tony</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜜汁帅气小彩蛋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>abc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陌云铃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>arT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忆丶醉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宇宙空间法师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛瑙星mnx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幻海</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Marvin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神烦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Joke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有酸萝卜别吃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m子会梦见花之暴君吗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘云金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天湮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持国产游戏，吾辈义不容辞！————读完本科自称硕士的沙雕的高质量网友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蟹老板的老公</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小小书童</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我知道我们没有缘分，这也不是我想要的结果，事与愿违，曾经我们都想好好的，即使现在我也是想要跟你好好的，虽然你看不见，但还是想留下这么一句话（可能会有人看到会觉得挺可笑的 确实挺幼稚的）十年的恋情，不希望给你带来生活的压力， 希望你快快乐乐的 这也是我一直给你说的 也是一直希望的—GQQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#00BFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉心糖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yeke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西瓜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幡因</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷灯蔷薇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗马皇帝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>观众老爷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZZZF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GOC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方糖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弱骨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星三西米露</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所行皆为何</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D3AdCa7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>summall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>句号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温情大白</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amomia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>禾Ray</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>惜源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿迟迟迟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纱布Sa_Official</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑白猪M82</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社畜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isarr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>什么时候君士坦丁十一世如闪电般归来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希望大家多多养猫，领养代替购买。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【前排征婚】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我和你一起爱左蓝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>男魔仙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏可以无限重开，可惜人生不能——活着吧，活着总比死了强。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#99ff99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早啊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢肥哥救我狗命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ed</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果可以的话希望人生重开后还能遇到你们</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清影昏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>散修少年</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>墨某</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eresh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ainavol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不识周树人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坠星灬追月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>juvucuc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深秋的七宗罪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>淋漓雨声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>废柴呀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天林灵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钱白安</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王牛子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dis114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺其自然</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linkanin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最佳演员路人甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐身。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊爷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彼岸星霜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小沈0421</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dorado</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小糊涂仙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姬子，不论重生多长次，我都等你回来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>离淘气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沐离</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>If what you need didn't exist. just create it.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五彩鸿鹄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#00ff00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为策划的脑洞和程序的脑细胞+发际线，干杯！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>策划让我写一句话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红烧二花肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顾熙豪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错过开关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞鸟掌门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>煮酒醉月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汉墨明华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人未尽”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡纸129</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shiny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钟离</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMFAH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Noah</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃酥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晨露微凉暮流光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若酷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剑绝轩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉然🥰我的嘉然🥰🥰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡尔西尔兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sbhehe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我永远喜欢阎魔爱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Achi-27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小僵尸是吃了跳跳糖么</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Muse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cxyfu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王柯南</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NIRVANA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加拿大刘亦菲Regina</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天边最远的云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路缃笺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酸菜鱼不酸嘴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>change-qrj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咸鱼粥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kkkm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏矢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iceking233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功夫不负有心人，8小时的执念，转世飞升，修仙之路漫漫，望道友们不要放弃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>祝愿游戏越做越好！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修罗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fish_Bubble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不用睡觉的柚子大魔王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#8600FF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KYLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孜然酥皮鸡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wujiongyu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加油站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物叔叔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忽忽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生生长流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雨過の天晴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄芥末酱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奈何</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青柠微凉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿三盖饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>許諾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤和艾莉欧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酷酷的内内</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kinko668</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大芋头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向日出许愿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低调De张扬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不说不懂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊公子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>璇瑰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>amisa_</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白讫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yaginya</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注嘉然，顿顿解馋❤️</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏可以无数次重来，但人生不行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小小小小冰冰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希望文字游戏越做越好 希望策划多多加班</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drown丶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mass Brain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wylszy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我也不知道我是谁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜音雪语</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还是叫hesy好了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新闻网小薇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏波poi丶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>汤姆毛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f0rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qwertyuiop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白勺光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我就一傻的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>俙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芭芭拉冲鸭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦香鸡腿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>YoKan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晨风</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花有重开日，人无在少年</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orphankun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希望游戏越做越好，Fight！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dfyx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷鱼雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的信仰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cccc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的那么多</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姜桐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>五月金小遥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南宇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜降</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qinyilinp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LQWQ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>航海家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸢鸣鸟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>determination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑稽树下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>萨姆饿了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>油炸丸子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恩维</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小羊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渊静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钛合金蚊子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱电用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是潇潇吖❀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Linda</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千织信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辞归</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关注嘉然，顿顿解馋😋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亖天荫亖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#ffccff</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1255,7 +2210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1265,6 +2220,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1541,7 +2499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D334"/>
+  <dimension ref="A1:D545"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="1" customWidth="1"/>
@@ -1561,7 +2519,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1660,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1668,10 +2626,10 @@
         <v>2</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1679,7 +2637,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1687,7 +2645,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1695,7 +2653,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1703,7 +2661,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1711,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -1722,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1730,7 +2688,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1738,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1746,7 +2704,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1754,7 +2712,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1762,7 +2720,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1770,7 +2728,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1778,7 +2736,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1786,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1794,10 +2752,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1805,7 +2763,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1813,7 +2771,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1821,7 +2779,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1829,7 +2787,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1837,7 +2795,7 @@
         <v>2</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1845,7 +2803,7 @@
         <v>2</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1853,7 +2811,7 @@
         <v>2</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1861,7 +2819,7 @@
         <v>2</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1869,7 +2827,7 @@
         <v>2</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1877,7 +2835,7 @@
         <v>2</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1885,7 +2843,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1893,7 +2851,7 @@
         <v>2</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1901,7 +2859,7 @@
         <v>2</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1909,7 +2867,7 @@
         <v>2</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1917,7 +2875,7 @@
         <v>2</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1925,7 +2883,7 @@
         <v>2</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1933,7 +2891,7 @@
         <v>2</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1941,7 +2899,7 @@
         <v>2</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1949,7 +2907,7 @@
         <v>2</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1957,7 +2915,7 @@
         <v>2</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1965,7 +2923,7 @@
         <v>2</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1973,7 +2931,7 @@
         <v>2</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1981,7 +2939,7 @@
         <v>2</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1989,7 +2947,7 @@
         <v>2</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1997,7 +2955,7 @@
         <v>2</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2005,7 +2963,7 @@
         <v>2</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2013,7 +2971,7 @@
         <v>2</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2021,7 +2979,7 @@
         <v>2</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2029,7 +2987,7 @@
         <v>2</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2037,7 +2995,7 @@
         <v>2</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2045,7 +3003,7 @@
         <v>2</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2053,7 +3011,7 @@
         <v>2</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2061,7 +3019,7 @@
         <v>2</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2069,7 +3027,7 @@
         <v>2</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2077,7 +3035,7 @@
         <v>2</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2085,7 +3043,7 @@
         <v>2</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2093,7 +3051,7 @@
         <v>2</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2101,7 +3059,7 @@
         <v>2</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2109,7 +3067,7 @@
         <v>2</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2117,7 +3075,7 @@
         <v>2</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2125,7 +3083,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2133,7 +3091,7 @@
         <v>2</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2141,7 +3099,7 @@
         <v>2</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2149,7 +3107,7 @@
         <v>2</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2157,7 +3115,7 @@
         <v>2</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2165,7 +3123,7 @@
         <v>2</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2173,10 +3131,10 @@
         <v>1</v>
       </c>
       <c r="B77" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2184,7 +3142,7 @@
         <v>2</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2192,7 +3150,7 @@
         <v>2</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2200,7 +3158,7 @@
         <v>2</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2208,7 +3166,7 @@
         <v>2</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2216,7 +3174,7 @@
         <v>2</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2224,10 +3182,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2235,7 +3193,7 @@
         <v>2</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2243,7 +3201,7 @@
         <v>2</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2251,7 +3209,7 @@
         <v>2</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2259,7 +3217,7 @@
         <v>2</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2267,7 +3225,7 @@
         <v>2</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2275,7 +3233,7 @@
         <v>2</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2283,7 +3241,7 @@
         <v>2</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2291,7 +3249,7 @@
         <v>2</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2299,7 +3257,7 @@
         <v>2</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2307,7 +3265,7 @@
         <v>2</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2315,7 +3273,7 @@
         <v>2</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2323,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2331,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2339,7 +3297,7 @@
         <v>2</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2347,7 +3305,7 @@
         <v>2</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2355,7 +3313,7 @@
         <v>2</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2363,7 +3321,7 @@
         <v>2</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2371,7 +3329,7 @@
         <v>2</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2379,7 +3337,7 @@
         <v>2</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2387,7 +3345,7 @@
         <v>2</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2395,7 +3353,7 @@
         <v>2</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2403,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2411,7 +3369,7 @@
         <v>2</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2419,7 +3377,7 @@
         <v>2</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2427,7 +3385,7 @@
         <v>2</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2435,7 +3393,7 @@
         <v>2</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2443,7 +3401,7 @@
         <v>2</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2451,10 +3409,10 @@
         <v>1</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2462,10 +3420,10 @@
         <v>1</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -2473,7 +3431,7 @@
         <v>2</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -2481,7 +3439,7 @@
         <v>2</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -2489,7 +3447,7 @@
         <v>2</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -2497,7 +3455,7 @@
         <v>2</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2505,7 +3463,7 @@
         <v>2</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -2513,7 +3471,7 @@
         <v>2</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2521,7 +3479,7 @@
         <v>2</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2529,7 +3487,7 @@
         <v>2</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -2537,7 +3495,7 @@
         <v>2</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -2545,10 +3503,10 @@
         <v>1</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -2556,7 +3514,7 @@
         <v>2</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -2564,7 +3522,7 @@
         <v>2</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -2572,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -2580,7 +3538,7 @@
         <v>2</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -2588,7 +3546,7 @@
         <v>2</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2596,7 +3554,7 @@
         <v>2</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2604,7 +3562,7 @@
         <v>2</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2612,7 +3570,7 @@
         <v>2</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2620,7 +3578,7 @@
         <v>2</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -2628,7 +3586,7 @@
         <v>2</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -2636,7 +3594,7 @@
         <v>2</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -2644,7 +3602,7 @@
         <v>2</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -2652,7 +3610,7 @@
         <v>2</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -2660,7 +3618,7 @@
         <v>2</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -2668,7 +3626,7 @@
         <v>2</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -2676,7 +3634,7 @@
         <v>2</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -2684,7 +3642,7 @@
         <v>2</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -2692,7 +3650,7 @@
         <v>2</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -2700,7 +3658,7 @@
         <v>2</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -2708,7 +3666,7 @@
         <v>2</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -2716,10 +3674,10 @@
         <v>1</v>
       </c>
       <c r="B143" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -2727,7 +3685,7 @@
         <v>2</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -2735,7 +3693,7 @@
         <v>2</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -2743,7 +3701,7 @@
         <v>2</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -2751,7 +3709,7 @@
         <v>2</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -2759,7 +3717,7 @@
         <v>2</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -2767,7 +3725,7 @@
         <v>2</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -2775,7 +3733,7 @@
         <v>2</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -2783,7 +3741,7 @@
         <v>2</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -2791,7 +3749,7 @@
         <v>2</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -2799,7 +3757,7 @@
         <v>2</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -2807,7 +3765,7 @@
         <v>2</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -2815,7 +3773,7 @@
         <v>2</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -2823,7 +3781,7 @@
         <v>2</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -2831,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -2839,7 +3797,7 @@
         <v>2</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -2847,7 +3805,7 @@
         <v>2</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -2855,7 +3813,7 @@
         <v>2</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -2863,7 +3821,7 @@
         <v>2</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -2871,7 +3829,7 @@
         <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -2879,7 +3837,7 @@
         <v>2</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -2887,10 +3845,10 @@
         <v>1</v>
       </c>
       <c r="B164" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -2898,7 +3856,7 @@
         <v>2</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -2906,7 +3864,7 @@
         <v>2</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -2914,7 +3872,7 @@
         <v>2</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -2922,10 +3880,10 @@
         <v>1</v>
       </c>
       <c r="B168" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -2933,10 +3891,10 @@
         <v>1</v>
       </c>
       <c r="B169" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C169" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -2944,10 +3902,10 @@
         <v>1</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -2955,7 +3913,7 @@
         <v>2</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -2963,7 +3921,7 @@
         <v>2</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -2971,7 +3929,7 @@
         <v>2</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -2979,7 +3937,7 @@
         <v>2</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -2987,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -2995,7 +3953,7 @@
         <v>2</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,7 +3961,7 @@
         <v>2</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3011,7 +3969,7 @@
         <v>2</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3019,7 +3977,7 @@
         <v>2</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -3027,7 +3985,7 @@
         <v>2</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -3035,7 +3993,7 @@
         <v>2</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -3043,7 +4001,7 @@
         <v>2</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -3051,7 +4009,7 @@
         <v>2</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -3059,7 +4017,7 @@
         <v>2</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -3067,7 +4025,7 @@
         <v>2</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -3075,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -3083,7 +4041,7 @@
         <v>2</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,7 +4049,7 @@
         <v>2</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -3099,7 +4057,7 @@
         <v>2</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -3107,7 +4065,7 @@
         <v>2</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -3115,10 +4073,10 @@
         <v>1</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -3126,7 +4084,7 @@
         <v>2</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -3134,7 +4092,7 @@
         <v>2</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -3142,7 +4100,7 @@
         <v>2</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3150,7 +4108,7 @@
         <v>2</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -3158,7 +4116,7 @@
         <v>2</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3166,7 +4124,7 @@
         <v>2</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -3174,7 +4132,7 @@
         <v>2</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -3182,7 +4140,7 @@
         <v>2</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3190,7 +4148,7 @@
         <v>2</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -3198,7 +4156,7 @@
         <v>2</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3206,7 +4164,7 @@
         <v>2</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -3214,7 +4172,7 @@
         <v>2</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -3222,7 +4180,7 @@
         <v>2</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3230,7 +4188,7 @@
         <v>2</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -3238,7 +4196,7 @@
         <v>2</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -3246,7 +4204,7 @@
         <v>2</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3254,7 +4212,7 @@
         <v>2</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -3262,7 +4220,7 @@
         <v>2</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -3270,7 +4228,7 @@
         <v>2</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,7 +4236,7 @@
         <v>2</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -3286,7 +4244,7 @@
         <v>2</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -3294,7 +4252,7 @@
         <v>2</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -3302,10 +4260,10 @@
         <v>1</v>
       </c>
       <c r="B214" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -3313,7 +4271,7 @@
         <v>2</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -3321,10 +4279,10 @@
         <v>1</v>
       </c>
       <c r="B216" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -3332,7 +4290,7 @@
         <v>2</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C217" s="2"/>
     </row>
@@ -3341,7 +4299,7 @@
         <v>2</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -3349,7 +4307,7 @@
         <v>2</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -3357,7 +4315,7 @@
         <v>2</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -3365,7 +4323,7 @@
         <v>2</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -3373,7 +4331,7 @@
         <v>2</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -3381,7 +4339,7 @@
         <v>2</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -3389,7 +4347,7 @@
         <v>2</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -3397,7 +4355,7 @@
         <v>2</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -3405,7 +4363,7 @@
         <v>2</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -3413,10 +4371,10 @@
         <v>1</v>
       </c>
       <c r="B227" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C227" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="C227" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -3424,7 +4382,7 @@
         <v>2</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -3432,7 +4390,7 @@
         <v>2</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -3440,7 +4398,7 @@
         <v>2</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -3448,7 +4406,7 @@
         <v>2</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -3456,7 +4414,7 @@
         <v>2</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -3464,7 +4422,7 @@
         <v>2</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -3472,7 +4430,7 @@
         <v>2</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -3480,7 +4438,7 @@
         <v>2</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -3488,7 +4446,7 @@
         <v>2</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -3496,7 +4454,7 @@
         <v>2</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -3504,7 +4462,7 @@
         <v>2</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -3512,7 +4470,7 @@
         <v>2</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -3520,7 +4478,7 @@
         <v>2</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -3528,7 +4486,7 @@
         <v>2</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -3536,10 +4494,10 @@
         <v>1</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -3547,7 +4505,7 @@
         <v>2</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -3555,7 +4513,7 @@
         <v>2</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -3563,7 +4521,7 @@
         <v>2</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -3571,7 +4529,7 @@
         <v>2</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -3579,7 +4537,7 @@
         <v>2</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -3587,7 +4545,7 @@
         <v>2</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -3595,7 +4553,7 @@
         <v>2</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -3603,7 +4561,7 @@
         <v>2</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -3611,7 +4569,7 @@
         <v>2</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,7 +4577,7 @@
         <v>2</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -3627,10 +4585,10 @@
         <v>1</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -3638,7 +4596,7 @@
         <v>2</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -3646,7 +4604,7 @@
         <v>2</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -3654,7 +4612,7 @@
         <v>2</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -3662,7 +4620,7 @@
         <v>2</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
@@ -3670,7 +4628,7 @@
         <v>2</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -3678,7 +4636,7 @@
         <v>2</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -3686,7 +4644,7 @@
         <v>2</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -3694,10 +4652,10 @@
         <v>1</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -3705,7 +4663,7 @@
         <v>2</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -3713,7 +4671,7 @@
         <v>2</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -3721,10 +4679,10 @@
         <v>1</v>
       </c>
       <c r="B264" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C264" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -3732,7 +4690,7 @@
         <v>2</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -3740,7 +4698,7 @@
         <v>2</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -3748,7 +4706,7 @@
         <v>2</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
@@ -3756,7 +4714,7 @@
         <v>2</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -3764,7 +4722,7 @@
         <v>2</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
@@ -3772,7 +4730,7 @@
         <v>2</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -3780,7 +4738,7 @@
         <v>2</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -3788,7 +4746,7 @@
         <v>2</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -3796,7 +4754,7 @@
         <v>2</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -3804,7 +4762,7 @@
         <v>2</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -3812,7 +4770,7 @@
         <v>2</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -3820,7 +4778,7 @@
         <v>2</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -3828,7 +4786,7 @@
         <v>2</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -3836,7 +4794,7 @@
         <v>2</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -3844,7 +4802,7 @@
         <v>2</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -3852,7 +4810,7 @@
         <v>2</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -3860,7 +4818,7 @@
         <v>2</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -3868,7 +4826,7 @@
         <v>2</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -3876,7 +4834,7 @@
         <v>2</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -3884,7 +4842,7 @@
         <v>2</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -3892,7 +4850,7 @@
         <v>2</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -3900,10 +4858,10 @@
         <v>1</v>
       </c>
       <c r="B286" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C286" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="C286" s="3" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -3911,7 +4869,7 @@
         <v>2</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -3919,7 +4877,7 @@
         <v>2</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -3927,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -3935,7 +4893,7 @@
         <v>2</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -3943,7 +4901,7 @@
         <v>2</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -3951,7 +4909,7 @@
         <v>2</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -3959,7 +4917,7 @@
         <v>2</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
@@ -3967,7 +4925,7 @@
         <v>2</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
@@ -3975,7 +4933,7 @@
         <v>2</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -3983,7 +4941,7 @@
         <v>2</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -3991,7 +4949,7 @@
         <v>2</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -3999,7 +4957,7 @@
         <v>2</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -4007,7 +4965,7 @@
         <v>2</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -4015,7 +4973,7 @@
         <v>2</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -4023,7 +4981,7 @@
         <v>2</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -4031,10 +4989,10 @@
         <v>1</v>
       </c>
       <c r="B302" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C302" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="C302" s="3" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -4042,7 +5000,7 @@
         <v>2</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
@@ -4050,7 +5008,7 @@
         <v>2</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
@@ -4058,7 +5016,7 @@
         <v>2</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
@@ -4066,7 +5024,7 @@
         <v>2</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
@@ -4074,7 +5032,7 @@
         <v>2</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
@@ -4082,7 +5040,7 @@
         <v>2</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
@@ -4090,7 +5048,7 @@
         <v>2</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
@@ -4098,7 +5056,7 @@
         <v>2</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
@@ -4106,7 +5064,7 @@
         <v>2</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
@@ -4114,7 +5072,7 @@
         <v>2</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
@@ -4122,7 +5080,7 @@
         <v>2</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
@@ -4130,7 +5088,7 @@
         <v>2</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
@@ -4138,7 +5096,7 @@
         <v>2</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
@@ -4146,7 +5104,7 @@
         <v>2</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
@@ -4154,7 +5112,7 @@
         <v>2</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
@@ -4162,7 +5120,7 @@
         <v>2</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
@@ -4170,7 +5128,7 @@
         <v>2</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
@@ -4178,7 +5136,7 @@
         <v>2</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
@@ -4186,7 +5144,7 @@
         <v>2</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
@@ -4194,7 +5152,7 @@
         <v>2</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -4202,7 +5160,7 @@
         <v>2</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
@@ -4210,7 +5168,7 @@
         <v>2</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
@@ -4218,7 +5176,7 @@
         <v>2</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
@@ -4226,7 +5184,7 @@
         <v>2</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -4234,7 +5192,7 @@
         <v>2</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
@@ -4242,7 +5200,7 @@
         <v>2</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
@@ -4250,7 +5208,7 @@
         <v>2</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
@@ -4258,7 +5216,7 @@
         <v>2</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -4266,7 +5224,7 @@
         <v>2</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -4274,7 +5232,7 @@
         <v>2</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
@@ -4282,7 +5240,7 @@
         <v>2</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
@@ -4290,7 +5248,1763 @@
         <v>2</v>
       </c>
       <c r="B334" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A335" s="1">
+        <v>2</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A336" s="1">
+        <v>2</v>
+      </c>
+      <c r="B336" s="3" t="s">
         <v>357</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="1">
+        <v>2</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="1">
+        <v>2</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="1">
+        <v>2</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="1">
+        <v>2</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="1">
+        <v>2</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="1">
+        <v>2</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="1">
+        <v>1</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="1">
+        <v>2</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="1">
+        <v>2</v>
+      </c>
+      <c r="B345" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="1">
+        <v>2</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="1">
+        <v>2</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="1">
+        <v>2</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="1">
+        <v>2</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="1">
+        <v>2</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="1">
+        <v>2</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="1">
+        <v>2</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>2</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>2</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" s="1">
+        <v>2</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" s="1">
+        <v>2</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" s="1">
+        <v>2</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" s="1">
+        <v>2</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" s="1">
+        <v>2</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" s="1">
+        <v>2</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" s="1">
+        <v>2</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" s="1">
+        <v>2</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" s="1">
+        <v>1</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" s="1">
+        <v>2</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" s="1">
+        <v>2</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" s="1">
+        <v>2</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D366" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" s="1">
+        <v>2</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368" s="1">
+        <v>2</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="1">
+        <v>2</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="1">
+        <v>2</v>
+      </c>
+      <c r="B370" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" s="1">
+        <v>2</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" s="1">
+        <v>2</v>
+      </c>
+      <c r="B372" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" s="1">
+        <v>2</v>
+      </c>
+      <c r="B373" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" s="1">
+        <v>2</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" s="1">
+        <v>2</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" s="1">
+        <v>2</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" s="1">
+        <v>2</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" s="1">
+        <v>2</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" s="1">
+        <v>2</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" s="1">
+        <v>2</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" s="1">
+        <v>2</v>
+      </c>
+      <c r="B381" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" s="1">
+        <v>2</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" s="1">
+        <v>1</v>
+      </c>
+      <c r="B383" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" s="1">
+        <v>2</v>
+      </c>
+      <c r="B384" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385" s="1">
+        <v>2</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386" s="1">
+        <v>2</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387" s="1">
+        <v>1</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388" s="1">
+        <v>2</v>
+      </c>
+      <c r="B388" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A389" s="1">
+        <v>2</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390" s="1">
+        <v>2</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" s="1">
+        <v>2</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392" s="1">
+        <v>1</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C392" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D392" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" s="1">
+        <v>2</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394" s="1">
+        <v>2</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395" s="1">
+        <v>2</v>
+      </c>
+      <c r="B395" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" s="1">
+        <v>2</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" s="1">
+        <v>2</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398" s="1">
+        <v>2</v>
+      </c>
+      <c r="B398" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399" s="1">
+        <v>1</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D399" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" s="1">
+        <v>2</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" s="1">
+        <v>2</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" s="1">
+        <v>2</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" s="1">
+        <v>2</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" s="1">
+        <v>2</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" s="1">
+        <v>2</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406" s="1">
+        <v>2</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" s="1">
+        <v>2</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" s="1">
+        <v>2</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" s="1">
+        <v>2</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" s="1">
+        <v>2</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" s="1">
+        <v>2</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" s="1">
+        <v>1</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" s="1">
+        <v>2</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" s="1">
+        <v>2</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" s="1">
+        <v>2</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" s="1">
+        <v>2</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417" s="1">
+        <v>2</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418" s="1">
+        <v>2</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A419" s="1">
+        <v>2</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A420" s="1">
+        <v>1</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C420" s="3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421" s="1">
+        <v>2</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A422" s="1">
+        <v>2</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A423" s="1">
+        <v>1</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A424" s="1">
+        <v>2</v>
+      </c>
+      <c r="B424" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A425" s="1">
+        <v>2</v>
+      </c>
+      <c r="B425" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A426" s="1">
+        <v>2</v>
+      </c>
+      <c r="B426" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A427" s="1">
+        <v>1</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A428" s="1">
+        <v>2</v>
+      </c>
+      <c r="B428" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C428" s="3"/>
+      <c r="D428" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A429" s="1">
+        <v>2</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C429" s="3"/>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A430" s="1">
+        <v>2</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A431" s="1">
+        <v>2</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A432" s="1">
+        <v>2</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A433" s="1">
+        <v>2</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A434" s="1">
+        <v>2</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A435" s="1">
+        <v>2</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A436" s="1">
+        <v>2</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A437" s="1">
+        <v>2</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A438" s="1">
+        <v>2</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A439" s="1">
+        <v>2</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A440" s="1">
+        <v>2</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A441" s="1">
+        <v>2</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A442" s="1">
+        <v>2</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A443" s="1">
+        <v>2</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A444" s="1">
+        <v>2</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A445" s="1">
+        <v>2</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A446" s="1">
+        <v>2</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A447" s="1">
+        <v>2</v>
+      </c>
+      <c r="B447" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A448" s="1">
+        <v>2</v>
+      </c>
+      <c r="B448" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A449" s="1">
+        <v>2</v>
+      </c>
+      <c r="B449" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A450" s="1">
+        <v>2</v>
+      </c>
+      <c r="B450" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A451" s="1">
+        <v>2</v>
+      </c>
+      <c r="B451" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A452" s="1">
+        <v>2</v>
+      </c>
+      <c r="B452" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A453" s="1">
+        <v>2</v>
+      </c>
+      <c r="B453" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A454" s="1">
+        <v>2</v>
+      </c>
+      <c r="B454" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A455" s="1">
+        <v>2</v>
+      </c>
+      <c r="B455" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A456" s="1">
+        <v>1</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A457" s="1">
+        <v>2</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A458" s="1">
+        <v>2</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A459" s="1">
+        <v>2</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A460" s="1">
+        <v>2</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A461" s="1">
+        <v>2</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A462" s="1">
+        <v>2</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A463" s="1">
+        <v>2</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A464" s="1">
+        <v>1</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C464" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A465" s="1">
+        <v>1</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C465" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A466" s="1">
+        <v>2</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A467" s="1">
+        <v>2</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A468" s="1">
+        <v>2</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="D468" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A469" s="1">
+        <v>2</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A470" s="1">
+        <v>2</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A471" s="1">
+        <v>2</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A472" s="1">
+        <v>2</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A473" s="1">
+        <v>2</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A474" s="1">
+        <v>2</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A475" s="1">
+        <v>2</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A476" s="1">
+        <v>2</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A477" s="1">
+        <v>2</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A478" s="1">
+        <v>2</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A479" s="1">
+        <v>2</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A480" s="1">
+        <v>2</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" s="1">
+        <v>2</v>
+      </c>
+      <c r="B481" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" s="1">
+        <v>2</v>
+      </c>
+      <c r="B482" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" s="1">
+        <v>2</v>
+      </c>
+      <c r="B483" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" s="1">
+        <v>2</v>
+      </c>
+      <c r="B484" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" s="1">
+        <v>1</v>
+      </c>
+      <c r="B485" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C485" s="3" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A486" s="1">
+        <v>2</v>
+      </c>
+      <c r="B486" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A487" s="1">
+        <v>2</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A488" s="1">
+        <v>2</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" s="1">
+        <v>2</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" s="1">
+        <v>2</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" s="1">
+        <v>2</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" s="1">
+        <v>2</v>
+      </c>
+      <c r="B492" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" s="1">
+        <v>2</v>
+      </c>
+      <c r="B493" s="3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" s="1">
+        <v>2</v>
+      </c>
+      <c r="B494" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" s="1">
+        <v>2</v>
+      </c>
+      <c r="B495" s="3" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" s="1">
+        <v>2</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" s="1">
+        <v>1</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C497" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" s="1">
+        <v>2</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" s="1">
+        <v>2</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" s="1">
+        <v>2</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" s="1">
+        <v>2</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502" s="1">
+        <v>2</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" s="1">
+        <v>2</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" s="1">
+        <v>2</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" s="1">
+        <v>2</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A506" s="1">
+        <v>2</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A507" s="1">
+        <v>2</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" s="1">
+        <v>2</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A509" s="1">
+        <v>1</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A510" s="1">
+        <v>2</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A511" s="1">
+        <v>2</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A512" s="1">
+        <v>2</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A513" s="1">
+        <v>2</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A514" s="1">
+        <v>2</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A515" s="1">
+        <v>2</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A516" s="1">
+        <v>2</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A517" s="1">
+        <v>2</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A518" s="1">
+        <v>2</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A519" s="1">
+        <v>2</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A520" s="1">
+        <v>2</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A521" s="1">
+        <v>2</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A522" s="1">
+        <v>2</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A523" s="1">
+        <v>2</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A524" s="1">
+        <v>2</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A525" s="1">
+        <v>2</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A526" s="1">
+        <v>2</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A527" s="1">
+        <v>2</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A528" s="1">
+        <v>2</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A529" s="1">
+        <v>2</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A530" s="1">
+        <v>2</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A531" s="1">
+        <v>2</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A532" s="1">
+        <v>2</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A533" s="1">
+        <v>2</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A534" s="1">
+        <v>2</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A535" s="1">
+        <v>2</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A536" s="1">
+        <v>2</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A537" s="1">
+        <v>2</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A538" s="1">
+        <v>2</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A539" s="1">
+        <v>2</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A540" s="1">
+        <v>2</v>
+      </c>
+      <c r="B540" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D540" s="3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A541" s="1">
+        <v>2</v>
+      </c>
+      <c r="B541" s="3" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A542" s="1">
+        <v>2</v>
+      </c>
+      <c r="B542" s="3" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A543" s="1">
+        <v>2</v>
+      </c>
+      <c r="B543" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A544" s="1">
+        <v>2</v>
+      </c>
+      <c r="B544" s="3" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A545" s="1">
+        <v>2</v>
+      </c>
+      <c r="B545" s="3" t="s">
+        <v>588</v>
       </c>
     </row>
   </sheetData>

--- a/games/life/data/specialthanks-afd.xlsx
+++ b/games/life/data/specialthanks-afd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\84694\Desktop\人生重来\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269F04D8-F596-496A-BF00-B8BE09FA7437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432123CF-23A5-4A7E-BD8A-CE4E8D292F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="606">
   <si>
     <t>group</t>
   </si>
@@ -2159,6 +2159,69 @@
   </si>
   <si>
     <t>#ffccff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迪拜小泥人</t>
+  </si>
+  <si>
+    <t>各自安好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多多支持国产游戏加油</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DialEctic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请让小翼在学会儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼饼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Golz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不吃香菜不订断更</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kxu3nive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罡风甚是喧嚣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Liangbi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>debuff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪莉丨星凌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>披坚执锐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2499,7 +2562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D545"/>
+  <dimension ref="A1:D560"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="1" customWidth="1"/>
@@ -6999,12 +7062,135 @@
         <v>587</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
         <v>2</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>588</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A546" s="1">
+        <v>2</v>
+      </c>
+      <c r="B546" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A547" s="1">
+        <v>2</v>
+      </c>
+      <c r="B547" s="3" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A548" s="1">
+        <v>1</v>
+      </c>
+      <c r="B548" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A549" s="1">
+        <v>2</v>
+      </c>
+      <c r="B549" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A550" s="1">
+        <v>2</v>
+      </c>
+      <c r="B550" s="3" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A551" s="1">
+        <v>2</v>
+      </c>
+      <c r="B551" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A552" s="1">
+        <v>2</v>
+      </c>
+      <c r="B552" s="3" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A553" s="1">
+        <v>2</v>
+      </c>
+      <c r="B553" s="3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A554" s="1">
+        <v>2</v>
+      </c>
+      <c r="B554" s="3" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A555" s="1">
+        <v>2</v>
+      </c>
+      <c r="B555" s="3" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A556" s="1">
+        <v>2</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A557" s="1">
+        <v>2</v>
+      </c>
+      <c r="B557" s="3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A558" s="1">
+        <v>2</v>
+      </c>
+      <c r="B558" s="3" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A559" s="1">
+        <v>2</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A560" s="1">
+        <v>2</v>
+      </c>
+      <c r="B560" s="3" t="s">
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/games/life/data/specialthanks-afd.xlsx
+++ b/games/life/data/specialthanks-afd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\84694\Desktop\人生重来\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432123CF-23A5-4A7E-BD8A-CE4E8D292F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC18B61-E844-4E8B-952C-C0850BACC964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="&gt;specialthanks&lt;arr&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="688">
   <si>
     <t>group</t>
   </si>
@@ -2222,6 +2222,334 @@
   </si>
   <si>
     <t>披坚执锐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寻麓-Cervoserĉo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是scp-114514</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xzny</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼鳃q</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星幻Larry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小狐狸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天门仙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>椰叶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oscar you</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤丸嘉人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梦絮Sigrid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>px5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eynaitty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我试着感受</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硫酸铜水合物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>努力的水哥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看我真挚的笑容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seka_L6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kotoha</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>达可达可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚沫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jjxxa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>妄人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pythagodzilla</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太白山野猪之光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劝飞光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樱年</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>薛定谔的猫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我愚蠢的欧豆豆哦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙二柱子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皓月长歌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逸云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那么可爱当然是__</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#ADFF2F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉然我真的好喜欢你啊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>楪之舞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山中迷路的小勘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月幵大fw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樱saber与魔人archer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>路痴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拓舟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>又找不到了qwq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>感谢你们为世界带来一些欢乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearMoon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>碳烤的咕咕蛋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鞠培雯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>想要内卷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝对不是楠桐的仓妖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无川手页的说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>￼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>靈間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑牙牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烧兔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晨曦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厕所</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0_fds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#FFFFFF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.71 8281 8284 5904</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石柱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MXS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迈阿密牛逼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JerryJiao</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙无芒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳伯壹仠肆佰伍拾叁世</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恶龙苏生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魏勇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mescaline茗零</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希希希土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>食光者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稻谷之骨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>七茗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harmony_Matrix.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两仪喵喵喵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其途</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加油呀小德，期待你的游戏大放异彩的那一天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i∈△</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可乐味的鸽子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子夜微雪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The_WhiteDragon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2562,16 +2890,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D560"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D637"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="42.21875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="42.25" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2585,7 +2913,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2596,7 +2924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2604,7 +2932,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -2612,7 +2940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -2620,7 +2948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -2628,7 +2956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -2636,7 +2964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -2644,7 +2972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -2652,7 +2980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -2660,7 +2988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -2668,7 +2996,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -2676,7 +3004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -2684,7 +3012,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -2695,7 +3023,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -2703,7 +3031,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -2711,7 +3039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -2719,7 +3047,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -2727,7 +3055,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -2738,7 +3066,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -2746,7 +3074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -2754,7 +3082,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>2</v>
       </c>
@@ -2762,7 +3090,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>2</v>
       </c>
@@ -2770,7 +3098,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -2778,7 +3106,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>2</v>
       </c>
@@ -2786,7 +3114,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>2</v>
       </c>
@@ -2794,7 +3122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>2</v>
       </c>
@@ -2802,7 +3130,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>2</v>
       </c>
@@ -2810,7 +3138,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -2821,7 +3149,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>2</v>
       </c>
@@ -2829,7 +3157,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>2</v>
       </c>
@@ -2837,7 +3165,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -2845,7 +3173,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>2</v>
       </c>
@@ -2853,7 +3181,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>2</v>
       </c>
@@ -2861,7 +3189,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>2</v>
       </c>
@@ -2869,7 +3197,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>2</v>
       </c>
@@ -2877,7 +3205,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>2</v>
       </c>
@@ -2885,7 +3213,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>2</v>
       </c>
@@ -2893,7 +3221,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>2</v>
       </c>
@@ -2901,7 +3229,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -2909,7 +3237,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>2</v>
       </c>
@@ -2917,7 +3245,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>2</v>
       </c>
@@ -2925,7 +3253,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>2</v>
       </c>
@@ -2933,7 +3261,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>2</v>
       </c>
@@ -2941,7 +3269,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>2</v>
       </c>
@@ -2949,7 +3277,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>2</v>
       </c>
@@ -2957,7 +3285,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>2</v>
       </c>
@@ -2965,7 +3293,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>2</v>
       </c>
@@ -2973,7 +3301,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>2</v>
       </c>
@@ -2981,7 +3309,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>2</v>
       </c>
@@ -2989,7 +3317,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>2</v>
       </c>
@@ -2997,7 +3325,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>2</v>
       </c>
@@ -3005,7 +3333,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>2</v>
       </c>
@@ -3013,7 +3341,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>2</v>
       </c>
@@ -3021,7 +3349,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>2</v>
       </c>
@@ -3029,7 +3357,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>2</v>
       </c>
@@ -3037,7 +3365,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>2</v>
       </c>
@@ -3045,7 +3373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>2</v>
       </c>
@@ -3053,7 +3381,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>2</v>
       </c>
@@ -3061,7 +3389,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>2</v>
       </c>
@@ -3069,7 +3397,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>2</v>
       </c>
@@ -3077,7 +3405,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>2</v>
       </c>
@@ -3085,7 +3413,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>2</v>
       </c>
@@ -3093,7 +3421,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>2</v>
       </c>
@@ -3101,7 +3429,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>2</v>
       </c>
@@ -3109,7 +3437,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>2</v>
       </c>
@@ -3117,7 +3445,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>2</v>
       </c>
@@ -3125,7 +3453,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>2</v>
       </c>
@@ -3133,7 +3461,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>2</v>
       </c>
@@ -3141,7 +3469,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>2</v>
       </c>
@@ -3149,7 +3477,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>2</v>
       </c>
@@ -3157,7 +3485,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>2</v>
       </c>
@@ -3165,7 +3493,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>2</v>
       </c>
@@ -3173,7 +3501,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>2</v>
       </c>
@@ -3181,7 +3509,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>2</v>
       </c>
@@ -3189,7 +3517,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>1</v>
       </c>
@@ -3200,7 +3528,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>2</v>
       </c>
@@ -3208,7 +3536,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>2</v>
       </c>
@@ -3216,7 +3544,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>2</v>
       </c>
@@ -3224,7 +3552,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>2</v>
       </c>
@@ -3232,7 +3560,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>2</v>
       </c>
@@ -3240,7 +3568,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>1</v>
       </c>
@@ -3251,7 +3579,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>2</v>
       </c>
@@ -3259,7 +3587,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>2</v>
       </c>
@@ -3267,7 +3595,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>2</v>
       </c>
@@ -3275,7 +3603,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>2</v>
       </c>
@@ -3283,7 +3611,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>2</v>
       </c>
@@ -3291,7 +3619,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>2</v>
       </c>
@@ -3299,7 +3627,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>2</v>
       </c>
@@ -3307,7 +3635,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>2</v>
       </c>
@@ -3315,7 +3643,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>2</v>
       </c>
@@ -3323,7 +3651,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>2</v>
       </c>
@@ -3331,7 +3659,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>2</v>
       </c>
@@ -3339,7 +3667,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>2</v>
       </c>
@@ -3347,7 +3675,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>2</v>
       </c>
@@ -3355,7 +3683,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>2</v>
       </c>
@@ -3363,7 +3691,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>2</v>
       </c>
@@ -3371,15 +3699,18 @@
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C99" s="3" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>2</v>
       </c>
@@ -3387,7 +3718,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>2</v>
       </c>
@@ -3395,7 +3726,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>2</v>
       </c>
@@ -3403,7 +3734,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>2</v>
       </c>
@@ -3411,7 +3742,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>2</v>
       </c>
@@ -3419,7 +3750,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>2</v>
       </c>
@@ -3427,7 +3758,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>2</v>
       </c>
@@ -3435,7 +3766,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>2</v>
       </c>
@@ -3443,7 +3774,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>2</v>
       </c>
@@ -3451,7 +3782,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>2</v>
       </c>
@@ -3459,7 +3790,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>2</v>
       </c>
@@ -3467,7 +3798,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>1</v>
       </c>
@@ -3478,7 +3809,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>1</v>
       </c>
@@ -3489,7 +3820,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>2</v>
       </c>
@@ -3497,7 +3828,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>2</v>
       </c>
@@ -3505,7 +3836,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>2</v>
       </c>
@@ -3513,7 +3844,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>2</v>
       </c>
@@ -3521,7 +3852,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>2</v>
       </c>
@@ -3529,7 +3860,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>2</v>
       </c>
@@ -3537,7 +3868,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>2</v>
       </c>
@@ -3545,7 +3876,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>2</v>
       </c>
@@ -3553,7 +3884,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>2</v>
       </c>
@@ -3561,7 +3892,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>1</v>
       </c>
@@ -3572,7 +3903,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>2</v>
       </c>
@@ -3580,7 +3911,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>2</v>
       </c>
@@ -3588,7 +3919,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>2</v>
       </c>
@@ -3596,7 +3927,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>2</v>
       </c>
@@ -3604,7 +3935,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>2</v>
       </c>
@@ -3612,7 +3943,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>2</v>
       </c>
@@ -3620,7 +3951,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>2</v>
       </c>
@@ -3628,7 +3959,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>2</v>
       </c>
@@ -3636,7 +3967,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>2</v>
       </c>
@@ -3644,7 +3975,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>2</v>
       </c>
@@ -3652,7 +3983,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>2</v>
       </c>
@@ -3660,7 +3991,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>2</v>
       </c>
@@ -3668,7 +3999,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>2</v>
       </c>
@@ -3676,7 +4007,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>2</v>
       </c>
@@ -3684,7 +4015,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>2</v>
       </c>
@@ -3692,7 +4023,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>2</v>
       </c>
@@ -3700,7 +4031,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>2</v>
       </c>
@@ -3708,7 +4039,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>2</v>
       </c>
@@ -3716,7 +4047,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>2</v>
       </c>
@@ -3724,7 +4055,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>2</v>
       </c>
@@ -3732,7 +4063,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>1</v>
       </c>
@@ -3743,7 +4074,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>2</v>
       </c>
@@ -3751,7 +4082,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>2</v>
       </c>
@@ -3759,7 +4090,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>2</v>
       </c>
@@ -3767,7 +4098,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>2</v>
       </c>
@@ -3775,7 +4106,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>2</v>
       </c>
@@ -3783,7 +4114,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>2</v>
       </c>
@@ -3791,7 +4122,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>2</v>
       </c>
@@ -3799,7 +4130,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>2</v>
       </c>
@@ -3807,7 +4138,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>2</v>
       </c>
@@ -3815,7 +4146,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>2</v>
       </c>
@@ -3823,7 +4154,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>2</v>
       </c>
@@ -3831,7 +4162,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>2</v>
       </c>
@@ -3839,7 +4170,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>2</v>
       </c>
@@ -3847,7 +4178,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>2</v>
       </c>
@@ -3855,7 +4186,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>2</v>
       </c>
@@ -3863,7 +4194,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>2</v>
       </c>
@@ -3871,7 +4202,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>2</v>
       </c>
@@ -3879,7 +4210,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>2</v>
       </c>
@@ -3887,7 +4218,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>2</v>
       </c>
@@ -3895,7 +4226,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>2</v>
       </c>
@@ -3903,7 +4234,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>1</v>
       </c>
@@ -3914,7 +4245,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>2</v>
       </c>
@@ -3922,7 +4253,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>2</v>
       </c>
@@ -3930,7 +4261,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>2</v>
       </c>
@@ -3938,7 +4269,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>1</v>
       </c>
@@ -3949,7 +4280,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>1</v>
       </c>
@@ -3960,7 +4291,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>1</v>
       </c>
@@ -3971,7 +4302,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>2</v>
       </c>
@@ -3979,7 +4310,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>2</v>
       </c>
@@ -3987,7 +4318,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>2</v>
       </c>
@@ -3995,7 +4326,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>2</v>
       </c>
@@ -4003,7 +4334,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>2</v>
       </c>
@@ -4011,7 +4342,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>2</v>
       </c>
@@ -4019,7 +4350,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>2</v>
       </c>
@@ -4027,7 +4358,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>2</v>
       </c>
@@ -4035,7 +4366,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>2</v>
       </c>
@@ -4043,7 +4374,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>2</v>
       </c>
@@ -4051,7 +4382,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>2</v>
       </c>
@@ -4059,7 +4390,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>2</v>
       </c>
@@ -4067,7 +4398,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>2</v>
       </c>
@@ -4075,7 +4406,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>2</v>
       </c>
@@ -4083,7 +4414,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>2</v>
       </c>
@@ -4091,7 +4422,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>2</v>
       </c>
@@ -4099,7 +4430,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>2</v>
       </c>
@@ -4107,7 +4438,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>2</v>
       </c>
@@ -4115,7 +4446,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>2</v>
       </c>
@@ -4123,7 +4454,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>2</v>
       </c>
@@ -4131,7 +4462,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>1</v>
       </c>
@@ -4142,7 +4473,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>2</v>
       </c>
@@ -4150,7 +4481,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>2</v>
       </c>
@@ -4158,7 +4489,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>2</v>
       </c>
@@ -4166,7 +4497,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>2</v>
       </c>
@@ -4174,7 +4505,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>2</v>
       </c>
@@ -4182,7 +4513,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>2</v>
       </c>
@@ -4190,7 +4521,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>2</v>
       </c>
@@ -4198,7 +4529,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>2</v>
       </c>
@@ -4206,7 +4537,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>2</v>
       </c>
@@ -4214,7 +4545,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>2</v>
       </c>
@@ -4222,7 +4553,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>2</v>
       </c>
@@ -4230,7 +4561,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>2</v>
       </c>
@@ -4238,7 +4569,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>2</v>
       </c>
@@ -4246,7 +4577,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>2</v>
       </c>
@@ -4254,7 +4585,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>2</v>
       </c>
@@ -4262,7 +4593,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>2</v>
       </c>
@@ -4270,7 +4601,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>2</v>
       </c>
@@ -4278,7 +4609,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>2</v>
       </c>
@@ -4286,7 +4617,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>2</v>
       </c>
@@ -4294,7 +4625,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>2</v>
       </c>
@@ -4302,7 +4633,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>2</v>
       </c>
@@ -4310,7 +4641,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>2</v>
       </c>
@@ -4318,7 +4649,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>1</v>
       </c>
@@ -4329,7 +4660,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>2</v>
       </c>
@@ -4337,7 +4668,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>1</v>
       </c>
@@ -4348,7 +4679,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>2</v>
       </c>
@@ -4357,7 +4688,7 @@
       </c>
       <c r="C217" s="2"/>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>2</v>
       </c>
@@ -4365,7 +4696,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>2</v>
       </c>
@@ -4373,7 +4704,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>2</v>
       </c>
@@ -4381,7 +4712,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>2</v>
       </c>
@@ -4389,7 +4720,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>2</v>
       </c>
@@ -4397,7 +4728,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>2</v>
       </c>
@@ -4405,7 +4736,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>2</v>
       </c>
@@ -4413,7 +4744,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>2</v>
       </c>
@@ -4421,7 +4752,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>2</v>
       </c>
@@ -4429,7 +4760,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>1</v>
       </c>
@@ -4440,7 +4771,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>2</v>
       </c>
@@ -4448,7 +4779,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>2</v>
       </c>
@@ -4456,7 +4787,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>2</v>
       </c>
@@ -4464,7 +4795,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>2</v>
       </c>
@@ -4472,7 +4803,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>2</v>
       </c>
@@ -4480,7 +4811,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>2</v>
       </c>
@@ -4488,7 +4819,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>2</v>
       </c>
@@ -4496,7 +4827,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>2</v>
       </c>
@@ -4504,7 +4835,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>2</v>
       </c>
@@ -4512,7 +4843,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>2</v>
       </c>
@@ -4520,7 +4851,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>2</v>
       </c>
@@ -4528,7 +4859,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>2</v>
       </c>
@@ -4536,7 +4867,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>2</v>
       </c>
@@ -4544,7 +4875,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>2</v>
       </c>
@@ -4552,7 +4883,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>1</v>
       </c>
@@ -4563,7 +4894,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>2</v>
       </c>
@@ -4571,7 +4902,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>2</v>
       </c>
@@ -4579,7 +4910,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>2</v>
       </c>
@@ -4587,7 +4918,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>2</v>
       </c>
@@ -4595,7 +4926,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>2</v>
       </c>
@@ -4603,7 +4934,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>2</v>
       </c>
@@ -4611,7 +4942,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>2</v>
       </c>
@@ -4619,7 +4950,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>2</v>
       </c>
@@ -4627,7 +4958,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>2</v>
       </c>
@@ -4635,7 +4966,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>2</v>
       </c>
@@ -4643,7 +4974,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>1</v>
       </c>
@@ -4654,7 +4985,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>2</v>
       </c>
@@ -4662,7 +4993,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>2</v>
       </c>
@@ -4670,7 +5001,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>2</v>
       </c>
@@ -4678,7 +5009,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>2</v>
       </c>
@@ -4686,7 +5017,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>2</v>
       </c>
@@ -4694,7 +5025,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>2</v>
       </c>
@@ -4702,7 +5033,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>2</v>
       </c>
@@ -4710,7 +5041,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>1</v>
       </c>
@@ -4721,7 +5052,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>2</v>
       </c>
@@ -4729,7 +5060,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>2</v>
       </c>
@@ -4737,7 +5068,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>1</v>
       </c>
@@ -4748,7 +5079,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>2</v>
       </c>
@@ -4756,7 +5087,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>2</v>
       </c>
@@ -4764,7 +5095,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>2</v>
       </c>
@@ -4772,7 +5103,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>2</v>
       </c>
@@ -4780,7 +5111,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>2</v>
       </c>
@@ -4788,7 +5119,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>2</v>
       </c>
@@ -4796,7 +5127,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>2</v>
       </c>
@@ -4804,7 +5135,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>2</v>
       </c>
@@ -4812,7 +5143,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>2</v>
       </c>
@@ -4820,7 +5151,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>2</v>
       </c>
@@ -4828,7 +5159,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>2</v>
       </c>
@@ -4836,7 +5167,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>2</v>
       </c>
@@ -4844,7 +5175,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>2</v>
       </c>
@@ -4852,7 +5183,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>2</v>
       </c>
@@ -4860,7 +5191,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>2</v>
       </c>
@@ -4868,7 +5199,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>2</v>
       </c>
@@ -4876,7 +5207,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>2</v>
       </c>
@@ -4884,7 +5215,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>2</v>
       </c>
@@ -4892,7 +5223,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>2</v>
       </c>
@@ -4900,7 +5231,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>2</v>
       </c>
@@ -4908,7 +5239,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>2</v>
       </c>
@@ -4916,7 +5247,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>1</v>
       </c>
@@ -4927,7 +5258,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>2</v>
       </c>
@@ -4935,7 +5266,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>2</v>
       </c>
@@ -4943,7 +5274,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>2</v>
       </c>
@@ -4951,7 +5282,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>2</v>
       </c>
@@ -4959,7 +5290,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>2</v>
       </c>
@@ -4967,7 +5298,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>2</v>
       </c>
@@ -4975,7 +5306,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>2</v>
       </c>
@@ -4983,7 +5314,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>2</v>
       </c>
@@ -4991,7 +5322,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>2</v>
       </c>
@@ -4999,7 +5330,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>2</v>
       </c>
@@ -5007,7 +5338,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>2</v>
       </c>
@@ -5015,7 +5346,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>2</v>
       </c>
@@ -5023,7 +5354,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>2</v>
       </c>
@@ -5031,7 +5362,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>2</v>
       </c>
@@ -5039,7 +5370,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>2</v>
       </c>
@@ -5047,7 +5378,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>1</v>
       </c>
@@ -5058,7 +5389,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>2</v>
       </c>
@@ -5066,7 +5397,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>2</v>
       </c>
@@ -5074,7 +5405,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>2</v>
       </c>
@@ -5082,7 +5413,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>2</v>
       </c>
@@ -5090,7 +5421,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>2</v>
       </c>
@@ -5098,7 +5429,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>2</v>
       </c>
@@ -5106,7 +5437,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>2</v>
       </c>
@@ -5114,7 +5445,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>2</v>
       </c>
@@ -5122,7 +5453,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>2</v>
       </c>
@@ -5130,7 +5461,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>2</v>
       </c>
@@ -5138,7 +5469,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>2</v>
       </c>
@@ -5146,7 +5477,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>2</v>
       </c>
@@ -5154,7 +5485,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>2</v>
       </c>
@@ -5162,7 +5493,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>2</v>
       </c>
@@ -5170,7 +5501,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>2</v>
       </c>
@@ -5178,7 +5509,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>2</v>
       </c>
@@ -5186,7 +5517,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>2</v>
       </c>
@@ -5194,7 +5525,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>2</v>
       </c>
@@ -5202,7 +5533,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>2</v>
       </c>
@@ -5210,7 +5541,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>2</v>
       </c>
@@ -5218,7 +5549,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>2</v>
       </c>
@@ -5226,7 +5557,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>2</v>
       </c>
@@ -5234,7 +5565,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>2</v>
       </c>
@@ -5242,7 +5573,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>2</v>
       </c>
@@ -5250,7 +5581,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>2</v>
       </c>
@@ -5258,7 +5589,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>2</v>
       </c>
@@ -5266,7 +5597,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>2</v>
       </c>
@@ -5274,7 +5605,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>2</v>
       </c>
@@ -5282,7 +5613,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>2</v>
       </c>
@@ -5290,7 +5621,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>2</v>
       </c>
@@ -5298,7 +5629,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>2</v>
       </c>
@@ -5306,7 +5637,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>2</v>
       </c>
@@ -5314,7 +5645,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>2</v>
       </c>
@@ -5322,7 +5653,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>2</v>
       </c>
@@ -5330,7 +5661,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>2</v>
       </c>
@@ -5338,7 +5669,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>2</v>
       </c>
@@ -5346,7 +5677,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>2</v>
       </c>
@@ -5354,7 +5685,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>2</v>
       </c>
@@ -5362,7 +5693,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>2</v>
       </c>
@@ -5370,7 +5701,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>2</v>
       </c>
@@ -5378,7 +5709,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>1</v>
       </c>
@@ -5389,7 +5720,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>2</v>
       </c>
@@ -5397,7 +5728,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>2</v>
       </c>
@@ -5405,7 +5736,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>2</v>
       </c>
@@ -5413,7 +5744,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>2</v>
       </c>
@@ -5421,7 +5752,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>2</v>
       </c>
@@ -5429,7 +5760,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>2</v>
       </c>
@@ -5437,7 +5768,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>2</v>
       </c>
@@ -5445,7 +5776,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>2</v>
       </c>
@@ -5453,7 +5784,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>2</v>
       </c>
@@ -5461,7 +5792,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>2</v>
       </c>
@@ -5469,7 +5800,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>2</v>
       </c>
@@ -5477,7 +5808,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>2</v>
       </c>
@@ -5485,7 +5816,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>2</v>
       </c>
@@ -5493,7 +5824,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>2</v>
       </c>
@@ -5501,7 +5832,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>2</v>
       </c>
@@ -5509,7 +5840,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>2</v>
       </c>
@@ -5517,7 +5848,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>2</v>
       </c>
@@ -5525,7 +5856,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>2</v>
       </c>
@@ -5533,7 +5864,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>2</v>
       </c>
@@ -5541,7 +5872,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>1</v>
       </c>
@@ -5552,7 +5883,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>2</v>
       </c>
@@ -5560,7 +5891,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>2</v>
       </c>
@@ -5568,7 +5899,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>2</v>
       </c>
@@ -5579,7 +5910,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>2</v>
       </c>
@@ -5587,7 +5918,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>2</v>
       </c>
@@ -5595,7 +5926,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>2</v>
       </c>
@@ -5603,7 +5934,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>2</v>
       </c>
@@ -5611,7 +5942,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>2</v>
       </c>
@@ -5619,7 +5950,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>2</v>
       </c>
@@ -5627,7 +5958,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>2</v>
       </c>
@@ -5635,7 +5966,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>2</v>
       </c>
@@ -5643,7 +5974,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>2</v>
       </c>
@@ -5651,7 +5982,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>2</v>
       </c>
@@ -5659,7 +5990,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>2</v>
       </c>
@@ -5667,7 +5998,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>2</v>
       </c>
@@ -5675,7 +6006,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>2</v>
       </c>
@@ -5683,7 +6014,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>2</v>
       </c>
@@ -5691,7 +6022,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>2</v>
       </c>
@@ -5699,7 +6030,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>2</v>
       </c>
@@ -5707,7 +6038,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>1</v>
       </c>
@@ -5718,7 +6049,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>2</v>
       </c>
@@ -5726,7 +6057,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>2</v>
       </c>
@@ -5734,7 +6065,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>2</v>
       </c>
@@ -5742,7 +6073,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>1</v>
       </c>
@@ -5753,7 +6084,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>2</v>
       </c>
@@ -5761,7 +6092,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>2</v>
       </c>
@@ -5769,7 +6100,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>2</v>
       </c>
@@ -5777,7 +6108,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>2</v>
       </c>
@@ -5785,7 +6116,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>1</v>
       </c>
@@ -5799,7 +6130,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>2</v>
       </c>
@@ -5807,7 +6138,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>2</v>
       </c>
@@ -5815,7 +6146,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>2</v>
       </c>
@@ -5823,7 +6154,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>2</v>
       </c>
@@ -5831,7 +6162,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>2</v>
       </c>
@@ -5839,7 +6170,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>2</v>
       </c>
@@ -5847,7 +6178,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>1</v>
       </c>
@@ -5861,7 +6192,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>2</v>
       </c>
@@ -5869,7 +6200,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>2</v>
       </c>
@@ -5877,7 +6208,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>2</v>
       </c>
@@ -5885,7 +6216,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>2</v>
       </c>
@@ -5893,7 +6224,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>2</v>
       </c>
@@ -5901,7 +6232,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>2</v>
       </c>
@@ -5909,7 +6240,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>2</v>
       </c>
@@ -5917,7 +6248,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>2</v>
       </c>
@@ -5925,7 +6256,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>2</v>
       </c>
@@ -5933,7 +6264,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>2</v>
       </c>
@@ -5941,7 +6272,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>2</v>
       </c>
@@ -5949,7 +6280,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>2</v>
       </c>
@@ -5957,7 +6288,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>1</v>
       </c>
@@ -5968,7 +6299,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>2</v>
       </c>
@@ -5976,7 +6307,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>2</v>
       </c>
@@ -5984,7 +6315,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>2</v>
       </c>
@@ -5992,7 +6323,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
         <v>2</v>
       </c>
@@ -6000,7 +6331,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
         <v>2</v>
       </c>
@@ -6008,7 +6339,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>2</v>
       </c>
@@ -6016,7 +6347,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>2</v>
       </c>
@@ -6024,7 +6355,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>1</v>
       </c>
@@ -6035,7 +6366,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>2</v>
       </c>
@@ -6043,7 +6374,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>2</v>
       </c>
@@ -6051,7 +6382,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>1</v>
       </c>
@@ -6062,7 +6393,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>2</v>
       </c>
@@ -6070,7 +6401,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>2</v>
       </c>
@@ -6078,7 +6409,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>2</v>
       </c>
@@ -6086,7 +6417,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>1</v>
       </c>
@@ -6097,7 +6428,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
         <v>2</v>
       </c>
@@ -6109,7 +6440,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
         <v>2</v>
       </c>
@@ -6118,7 +6449,7 @@
       </c>
       <c r="C429" s="3"/>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
         <v>2</v>
       </c>
@@ -6126,7 +6457,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
         <v>2</v>
       </c>
@@ -6134,7 +6465,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
         <v>2</v>
       </c>
@@ -6142,7 +6473,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
         <v>2</v>
       </c>
@@ -6150,7 +6481,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
         <v>2</v>
       </c>
@@ -6158,7 +6489,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
         <v>2</v>
       </c>
@@ -6166,7 +6497,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
         <v>2</v>
       </c>
@@ -6174,7 +6505,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
         <v>2</v>
       </c>
@@ -6182,7 +6513,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
         <v>2</v>
       </c>
@@ -6190,7 +6521,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
         <v>2</v>
       </c>
@@ -6198,7 +6529,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
         <v>2</v>
       </c>
@@ -6206,7 +6537,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
         <v>2</v>
       </c>
@@ -6214,7 +6545,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
         <v>2</v>
       </c>
@@ -6222,7 +6553,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
         <v>2</v>
       </c>
@@ -6230,7 +6561,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
         <v>2</v>
       </c>
@@ -6238,7 +6569,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
         <v>2</v>
       </c>
@@ -6246,7 +6577,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
         <v>2</v>
       </c>
@@ -6254,7 +6585,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
         <v>2</v>
       </c>
@@ -6262,7 +6593,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
         <v>2</v>
       </c>
@@ -6270,7 +6601,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
         <v>2</v>
       </c>
@@ -6278,7 +6609,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
         <v>2</v>
       </c>
@@ -6286,7 +6617,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
         <v>2</v>
       </c>
@@ -6294,7 +6625,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
         <v>2</v>
       </c>
@@ -6302,7 +6633,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
         <v>2</v>
       </c>
@@ -6310,7 +6641,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
         <v>2</v>
       </c>
@@ -6318,7 +6649,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
         <v>2</v>
       </c>
@@ -6326,7 +6657,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
         <v>1</v>
       </c>
@@ -6337,7 +6668,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
         <v>2</v>
       </c>
@@ -6345,7 +6676,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
         <v>2</v>
       </c>
@@ -6353,7 +6684,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
         <v>2</v>
       </c>
@@ -6361,7 +6692,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
         <v>2</v>
       </c>
@@ -6369,7 +6700,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
         <v>2</v>
       </c>
@@ -6377,7 +6708,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
         <v>2</v>
       </c>
@@ -6385,7 +6716,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
         <v>2</v>
       </c>
@@ -6393,7 +6724,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="1">
         <v>1</v>
       </c>
@@ -6404,7 +6735,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A465" s="1">
         <v>1</v>
       </c>
@@ -6415,7 +6746,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A466" s="1">
         <v>2</v>
       </c>
@@ -6423,7 +6754,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A467" s="1">
         <v>2</v>
       </c>
@@ -6431,7 +6762,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A468" s="1">
         <v>2</v>
       </c>
@@ -6442,7 +6773,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A469" s="1">
         <v>2</v>
       </c>
@@ -6450,7 +6781,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A470" s="1">
         <v>2</v>
       </c>
@@ -6458,7 +6789,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A471" s="1">
         <v>2</v>
       </c>
@@ -6466,7 +6797,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A472" s="1">
         <v>2</v>
       </c>
@@ -6474,7 +6805,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A473" s="1">
         <v>2</v>
       </c>
@@ -6482,7 +6813,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A474" s="1">
         <v>2</v>
       </c>
@@ -6490,7 +6821,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A475" s="1">
         <v>2</v>
       </c>
@@ -6498,7 +6829,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A476" s="1">
         <v>2</v>
       </c>
@@ -6506,7 +6837,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A477" s="1">
         <v>2</v>
       </c>
@@ -6514,7 +6845,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A478" s="1">
         <v>2</v>
       </c>
@@ -6522,7 +6853,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A479" s="1">
         <v>2</v>
       </c>
@@ -6530,7 +6861,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A480" s="1">
         <v>2</v>
       </c>
@@ -6538,7 +6869,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A481" s="1">
         <v>2</v>
       </c>
@@ -6546,7 +6877,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A482" s="1">
         <v>2</v>
       </c>
@@ -6554,7 +6885,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A483" s="1">
         <v>2</v>
       </c>
@@ -6562,7 +6893,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A484" s="1">
         <v>2</v>
       </c>
@@ -6570,7 +6901,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A485" s="1">
         <v>1</v>
       </c>
@@ -6581,7 +6912,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="1">
         <v>2</v>
       </c>
@@ -6589,7 +6920,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A487" s="1">
         <v>2</v>
       </c>
@@ -6597,7 +6928,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A488" s="1">
         <v>2</v>
       </c>
@@ -6605,7 +6936,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A489" s="1">
         <v>2</v>
       </c>
@@ -6613,7 +6944,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A490" s="1">
         <v>2</v>
       </c>
@@ -6621,7 +6952,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A491" s="1">
         <v>2</v>
       </c>
@@ -6629,7 +6960,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A492" s="1">
         <v>2</v>
       </c>
@@ -6637,7 +6968,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A493" s="1">
         <v>2</v>
       </c>
@@ -6645,7 +6976,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A494" s="1">
         <v>2</v>
       </c>
@@ -6653,7 +6984,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A495" s="1">
         <v>2</v>
       </c>
@@ -6661,7 +6992,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A496" s="1">
         <v>2</v>
       </c>
@@ -6669,7 +7000,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="1">
         <v>1</v>
       </c>
@@ -6680,7 +7011,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A498" s="1">
         <v>2</v>
       </c>
@@ -6688,7 +7019,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A499" s="1">
         <v>2</v>
       </c>
@@ -6696,7 +7027,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A500" s="1">
         <v>2</v>
       </c>
@@ -6704,7 +7035,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A501" s="1">
         <v>2</v>
       </c>
@@ -6712,7 +7043,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A502" s="1">
         <v>2</v>
       </c>
@@ -6720,7 +7051,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A503" s="1">
         <v>2</v>
       </c>
@@ -6728,7 +7059,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A504" s="1">
         <v>2</v>
       </c>
@@ -6736,7 +7067,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A505" s="1">
         <v>2</v>
       </c>
@@ -6744,7 +7075,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A506" s="1">
         <v>2</v>
       </c>
@@ -6752,7 +7083,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A507" s="1">
         <v>2</v>
       </c>
@@ -6760,7 +7091,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="1">
         <v>2</v>
       </c>
@@ -6768,7 +7099,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A509" s="1">
         <v>1</v>
       </c>
@@ -6779,7 +7110,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A510" s="1">
         <v>2</v>
       </c>
@@ -6787,7 +7118,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A511" s="1">
         <v>2</v>
       </c>
@@ -6795,7 +7126,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A512" s="1">
         <v>2</v>
       </c>
@@ -6803,7 +7134,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" s="1">
         <v>2</v>
       </c>
@@ -6811,7 +7142,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" s="1">
         <v>2</v>
       </c>
@@ -6819,7 +7150,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" s="1">
         <v>2</v>
       </c>
@@ -6827,7 +7158,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" s="1">
         <v>2</v>
       </c>
@@ -6835,7 +7166,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" s="1">
         <v>2</v>
       </c>
@@ -6843,7 +7174,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" s="1">
         <v>2</v>
       </c>
@@ -6851,7 +7182,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" s="1">
         <v>2</v>
       </c>
@@ -6859,7 +7190,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" s="1">
         <v>2</v>
       </c>
@@ -6867,7 +7198,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" s="1">
         <v>2</v>
       </c>
@@ -6875,7 +7206,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" s="1">
         <v>2</v>
       </c>
@@ -6883,7 +7214,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" s="1">
         <v>2</v>
       </c>
@@ -6891,7 +7222,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" s="1">
         <v>2</v>
       </c>
@@ -6899,7 +7230,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" s="1">
         <v>2</v>
       </c>
@@ -6907,7 +7238,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" s="1">
         <v>2</v>
       </c>
@@ -6915,7 +7246,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" s="1">
         <v>2</v>
       </c>
@@ -6923,7 +7254,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" s="1">
         <v>2</v>
       </c>
@@ -6931,7 +7262,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A529" s="1">
         <v>2</v>
       </c>
@@ -6939,7 +7270,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A530" s="1">
         <v>2</v>
       </c>
@@ -6947,7 +7278,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A531" s="1">
         <v>2</v>
       </c>
@@ -6955,7 +7286,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A532" s="1">
         <v>2</v>
       </c>
@@ -6963,7 +7294,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A533" s="1">
         <v>2</v>
       </c>
@@ -6971,7 +7302,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A534" s="1">
         <v>2</v>
       </c>
@@ -6979,7 +7310,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A535" s="1">
         <v>2</v>
       </c>
@@ -6987,7 +7318,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A536" s="1">
         <v>2</v>
       </c>
@@ -6995,7 +7326,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
         <v>2</v>
       </c>
@@ -7003,7 +7334,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A538" s="1">
         <v>2</v>
       </c>
@@ -7011,7 +7342,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A539" s="1">
         <v>2</v>
       </c>
@@ -7019,7 +7350,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A540" s="1">
         <v>2</v>
       </c>
@@ -7030,7 +7361,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A541" s="1">
         <v>2</v>
       </c>
@@ -7038,7 +7369,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A542" s="1">
         <v>2</v>
       </c>
@@ -7046,7 +7377,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A543" s="1">
         <v>2</v>
       </c>
@@ -7054,7 +7385,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A544" s="1">
         <v>2</v>
       </c>
@@ -7062,7 +7393,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A545" s="1">
         <v>2</v>
       </c>
@@ -7070,7 +7401,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A546" s="1">
         <v>2</v>
       </c>
@@ -7078,7 +7409,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A547" s="1">
         <v>2</v>
       </c>
@@ -7086,7 +7417,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A548" s="1">
         <v>1</v>
       </c>
@@ -7097,7 +7428,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A549" s="1">
         <v>2</v>
       </c>
@@ -7105,7 +7436,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A550" s="1">
         <v>2</v>
       </c>
@@ -7113,7 +7444,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A551" s="1">
         <v>2</v>
       </c>
@@ -7121,7 +7452,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="1">
         <v>2</v>
       </c>
@@ -7129,7 +7460,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A553" s="1">
         <v>2</v>
       </c>
@@ -7137,7 +7468,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A554" s="1">
         <v>2</v>
       </c>
@@ -7145,7 +7476,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A555" s="1">
         <v>2</v>
       </c>
@@ -7153,7 +7484,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A556" s="1">
         <v>2</v>
       </c>
@@ -7161,7 +7492,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A557" s="1">
         <v>2</v>
       </c>
@@ -7169,7 +7500,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A558" s="1">
         <v>2</v>
       </c>
@@ -7177,7 +7508,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A559" s="1">
         <v>2</v>
       </c>
@@ -7185,12 +7516,640 @@
         <v>604</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A560" s="1">
         <v>2</v>
       </c>
       <c r="B560" s="3" t="s">
         <v>605</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A561" s="1">
+        <v>2</v>
+      </c>
+      <c r="B561" s="3" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A562" s="1">
+        <v>2</v>
+      </c>
+      <c r="B562" s="3" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A563" s="1">
+        <v>2</v>
+      </c>
+      <c r="B563" s="3" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A564" s="1">
+        <v>2</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A565" s="1">
+        <v>2</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A566" s="1">
+        <v>2</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A567" s="1">
+        <v>2</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A568" s="1">
+        <v>2</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A569" s="1">
+        <v>2</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A570" s="1">
+        <v>2</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A571" s="1">
+        <v>2</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A572" s="1">
+        <v>2</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A573" s="1">
+        <v>2</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A574" s="1">
+        <v>2</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A575" s="1">
+        <v>2</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A576" s="1">
+        <v>2</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A577" s="1">
+        <v>2</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A578" s="1">
+        <v>2</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A579" s="1">
+        <v>2</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A580" s="1">
+        <v>2</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A581" s="1">
+        <v>2</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A582" s="1">
+        <v>2</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A583" s="1">
+        <v>2</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A584" s="1">
+        <v>2</v>
+      </c>
+      <c r="B584" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A585" s="1">
+        <v>2</v>
+      </c>
+      <c r="B585" s="3" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A586" s="1">
+        <v>2</v>
+      </c>
+      <c r="B586" s="3" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A587" s="1">
+        <v>2</v>
+      </c>
+      <c r="B587" s="3" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A588" s="1">
+        <v>2</v>
+      </c>
+      <c r="B588" s="3" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A589" s="1">
+        <v>2</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A590" s="1">
+        <v>2</v>
+      </c>
+      <c r="B590" s="3" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A591" s="1">
+        <v>2</v>
+      </c>
+      <c r="B591" s="3" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A592" s="1">
+        <v>2</v>
+      </c>
+      <c r="B592" s="3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A593" s="1">
+        <v>2</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A594" s="1">
+        <v>2</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D594" s="3" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A595" s="1">
+        <v>2</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A596" s="1">
+        <v>2</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A597" s="1">
+        <v>2</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A598" s="1">
+        <v>2</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A599" s="1">
+        <v>2</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A600" s="1">
+        <v>2</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A601" s="1">
+        <v>2</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A602" s="1">
+        <v>2</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A603" s="1">
+        <v>2</v>
+      </c>
+      <c r="B603" s="3" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A604" s="1">
+        <v>2</v>
+      </c>
+      <c r="B604" s="3" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A605" s="1">
+        <v>2</v>
+      </c>
+      <c r="B605" s="3" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A606" s="1">
+        <v>2</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A607" s="1">
+        <v>2</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A608" s="1">
+        <v>2</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A609" s="1">
+        <v>2</v>
+      </c>
+      <c r="B609" s="3" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A610" s="1">
+        <v>2</v>
+      </c>
+      <c r="B610" s="3" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A611" s="1">
+        <v>2</v>
+      </c>
+      <c r="B611" s="3" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A612" s="1">
+        <v>2</v>
+      </c>
+      <c r="B612" s="3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A613" s="1">
+        <v>2</v>
+      </c>
+      <c r="B613" s="3" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A614" s="1">
+        <v>2</v>
+      </c>
+      <c r="B614" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A615" s="1">
+        <v>1</v>
+      </c>
+      <c r="B615" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C615" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D615" s="3" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A616" s="1">
+        <v>2</v>
+      </c>
+      <c r="B616" s="3" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A617" s="1">
+        <v>2</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A618" s="1">
+        <v>2</v>
+      </c>
+      <c r="B618" s="3" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A619" s="1">
+        <v>2</v>
+      </c>
+      <c r="B619" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A620" s="1">
+        <v>2</v>
+      </c>
+      <c r="B620" s="3" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A621" s="1">
+        <v>2</v>
+      </c>
+      <c r="B621" s="3" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A622" s="1">
+        <v>2</v>
+      </c>
+      <c r="B622" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A623" s="1">
+        <v>2</v>
+      </c>
+      <c r="B623" s="3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A624" s="1">
+        <v>2</v>
+      </c>
+      <c r="B624" s="3" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A625" s="1">
+        <v>2</v>
+      </c>
+      <c r="B625" s="3" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A626" s="1">
+        <v>2</v>
+      </c>
+      <c r="B626" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A627" s="1">
+        <v>2</v>
+      </c>
+      <c r="B627" s="3" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A628" s="1">
+        <v>2</v>
+      </c>
+      <c r="B628" s="3" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A629" s="1">
+        <v>2</v>
+      </c>
+      <c r="B629" s="3" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A630" s="1">
+        <v>2</v>
+      </c>
+      <c r="B630" s="3" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A631" s="1">
+        <v>2</v>
+      </c>
+      <c r="B631" s="3" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A632" s="1">
+        <v>1</v>
+      </c>
+      <c r="B632" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A633" s="1">
+        <v>2</v>
+      </c>
+      <c r="B633" s="3" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A634" s="1">
+        <v>2</v>
+      </c>
+      <c r="B634" s="3" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A635" s="1">
+        <v>2</v>
+      </c>
+      <c r="B635" s="3" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A636" s="1">
+        <v>2</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A637" s="1">
+        <v>2</v>
+      </c>
+      <c r="B637" s="3" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>
